--- a/Sales Sample File 2025.xlsx
+++ b/Sales Sample File 2025.xlsx
@@ -5,15 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://publicisgroupe-my.sharepoint.com/personal/gioivard_publicisgroupe_net/Documents/Desktop/Mcdonalds/GitHub/Power BI/QSR-DEV/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://publicisgroupe-my.sharepoint.com/personal/gioivard_publicisgroupe_net/Documents/Desktop/Mcdonalds/GitHub/Power BI/QSR-TEST/QSR-TEST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15765841-2C92-4FE0-B862-EF44A487940A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{15765841-2C92-4FE0-B862-EF44A487940A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06F2AB97-8BC8-438F-8452-CC19AED5DD19}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9BE37F5C-72F5-4934-8EDF-54B3D168F3FC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{9BE37F5C-72F5-4934-8EDF-54B3D168F3FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>reportingid</t>
   </si>
@@ -45,6 +47,12 @@
   </si>
   <si>
     <t>totalamount</t>
+  </si>
+  <si>
+    <t>added this sheet for testing</t>
+  </si>
+  <si>
+    <t>then thi sheet</t>
   </si>
 </sst>
 </file>
@@ -1350,4 +1358,34 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B8282FC-2AA8-4693-A500-C3028693E12F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB6D9CA6-C9BB-42EC-A198-29B29B61C3AD}">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>